--- a/RunningTimeRecord.xlsx
+++ b/RunningTimeRecord.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECE0429-BB7B-4E72-B301-B00492B47215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62499079-4B7C-42CF-B560-9A89B60CE0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
@@ -85,15 +85,33 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -101,11 +119,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -117,7 +150,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,19 +444,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="7" width="22.6328125" customWidth="1"/>
+    <col min="1" max="7" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -425,7 +470,7 @@
       </c>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -448,14 +493,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>10000000</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>4.1623950000000001</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <f>5.247637+B5</f>
         <v>9.4100320000000011</v>
       </c>
@@ -472,14 +517,14 @@
         <v>6.7915789999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>15000000</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>7.627834</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <f>8.309336+B6</f>
         <v>15.93717</v>
       </c>
@@ -496,14 +541,14 @@
         <v>9.9260079999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>20000000</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>11.705761000000001</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <f>10.886813+B7</f>
         <v>22.592573999999999</v>
       </c>
@@ -520,14 +565,14 @@
         <v>13.217007000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>25000000</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>15.923990999999999</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8">
         <f>12.898962+B8</f>
         <v>28.822952999999998</v>
       </c>
@@ -544,14 +589,14 @@
         <v>16.510265</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>30000000</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>20.415963000000001</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9">
         <f>15.466003+B9</f>
         <v>35.881966000000006</v>
       </c>
@@ -568,14 +613,14 @@
         <v>19.987759</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>35000000</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>25.999472999999998</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10">
         <f>20.972771+B10</f>
         <v>46.972244000000003</v>
       </c>
@@ -592,14 +637,14 @@
         <v>23.276264000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>40000000</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>32.189481999999998</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11">
         <f>25.823072+B11</f>
         <v>58.012553999999994</v>
       </c>
@@ -616,14 +661,14 @@
         <v>25.529710000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>45000000</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12">
         <v>37.943916999999999</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12">
         <f>29.341272+B12</f>
         <v>67.285189000000003</v>
       </c>
@@ -640,14 +685,14 @@
         <v>29.8569</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>50000000</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13">
         <v>46.904995</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13">
         <f>31.02748+B13</f>
         <v>77.932474999999997</v>
       </c>
@@ -664,112 +709,221 @@
         <v>35.428055000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B16" s="4" t="s">
+    <row r="16" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4" t="s">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4" t="s">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+    <row r="18" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11">
         <v>10000000</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12">
+        <v>0.188636</v>
+      </c>
+      <c r="E18" s="12">
+        <v>4.9392230000000001</v>
+      </c>
+      <c r="F18" s="12">
+        <v>1.384317</v>
+      </c>
+      <c r="G18" s="12">
+        <v>6.1650879999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
         <v>15000000</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+      <c r="D19" s="5">
+        <v>0.30043999999999998</v>
+      </c>
+      <c r="E19" s="5">
+        <v>8.0359610000000004</v>
+      </c>
+      <c r="F19" s="5">
+        <v>2.5880679999999998</v>
+      </c>
+      <c r="G19" s="5">
+        <v>10.625273</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11">
         <v>20000000</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12">
+        <v>0.446938</v>
+      </c>
+      <c r="E20" s="12">
+        <v>10.283652</v>
+      </c>
+      <c r="F20" s="12">
+        <v>2.7769949999999999</v>
+      </c>
+      <c r="G20" s="12">
+        <v>12.613759999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
         <v>25000000</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+      <c r="D21" s="5">
+        <v>0.60850400000000004</v>
+      </c>
+      <c r="E21" s="5">
+        <v>11.7872</v>
+      </c>
+      <c r="F21" s="5">
+        <v>3.9838559999999998</v>
+      </c>
+      <c r="G21" s="5">
+        <v>16.541592000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11">
         <v>30000000</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12">
+        <v>0.78666400000000003</v>
+      </c>
+      <c r="E22" s="12">
+        <v>16.037421999999999</v>
+      </c>
+      <c r="F22" s="12">
+        <v>5.5545479999999996</v>
+      </c>
+      <c r="G22" s="12">
+        <v>19.275448000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
         <v>35000000</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+      <c r="D23" s="5">
+        <v>0.97917200000000004</v>
+      </c>
+      <c r="E23" s="5">
+        <v>16.859352000000001</v>
+      </c>
+      <c r="F23" s="5">
+        <v>6.1012940000000002</v>
+      </c>
+      <c r="G23" s="5">
+        <v>22.961316</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
         <v>40000000</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12">
+        <v>1.135345</v>
+      </c>
+      <c r="E24" s="12">
+        <v>22.491413999999999</v>
+      </c>
+      <c r="F24" s="12">
+        <v>6.5744150000000001</v>
+      </c>
+      <c r="G24" s="12">
+        <v>25.531298</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10">
         <v>45000000</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
+      <c r="D25" s="5">
+        <v>1.3597349999999999</v>
+      </c>
+      <c r="E25" s="5">
+        <v>24.880361000000001</v>
+      </c>
+      <c r="F25" s="5">
+        <v>7.7472500000000002</v>
+      </c>
+      <c r="G25" s="5">
+        <v>31.823687</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11">
         <v>50000000</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12">
+        <v>1.552114</v>
+      </c>
+      <c r="E26" s="12">
+        <v>25.495045000000001</v>
+      </c>
+      <c r="F26" s="12">
+        <v>9.0593489999999992</v>
+      </c>
+      <c r="G26" s="12">
+        <v>31.419589999999999</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -787,19 +941,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2B590C-628F-42C3-BA14-2549B4CA5D44}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="22.6328125" customWidth="1"/>
-    <col min="4" max="4" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -809,7 +963,7 @@
       </c>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -826,7 +980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -843,7 +997,7 @@
         <v>7.352087</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -860,7 +1014,7 @@
         <v>6.3732189999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>8</v>
       </c>
@@ -877,7 +1031,7 @@
         <v>6.6873300000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>16</v>
       </c>
@@ -894,7 +1048,7 @@
         <v>6.7687369999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>32</v>
       </c>
@@ -911,7 +1065,7 @@
         <v>7.2332419999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>64</v>
       </c>
@@ -928,15 +1082,15 @@
         <v>6.5813569999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>9</v>
       </c>
@@ -946,7 +1100,7 @@
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>3</v>
       </c>
@@ -963,34 +1117,106 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B16">
+        <v>1.7803150000000001</v>
+      </c>
+      <c r="C16">
+        <v>7.0986909999999996</v>
+      </c>
+      <c r="D16">
+        <v>1.540073</v>
+      </c>
+      <c r="E16">
+        <v>6.6633519999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B17">
+        <v>0.91214399999999995</v>
+      </c>
+      <c r="C17">
+        <v>5.3931120000000004</v>
+      </c>
+      <c r="D17">
+        <v>1.2319119999999999</v>
+      </c>
+      <c r="E17">
+        <v>6.6738819999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B18">
+        <v>0.41222500000000001</v>
+      </c>
+      <c r="C18">
+        <v>5.5883979999999998</v>
+      </c>
+      <c r="D18">
+        <v>1.4754229999999999</v>
+      </c>
+      <c r="E18">
+        <v>6.1407610000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B19">
+        <v>0.248222</v>
+      </c>
+      <c r="C19">
+        <v>5.4797409999999998</v>
+      </c>
+      <c r="D19">
+        <v>1.988049</v>
+      </c>
+      <c r="E19">
+        <v>7.3005849999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B20">
+        <v>0.18618000000000001</v>
+      </c>
+      <c r="C20">
+        <v>4.9896700000000003</v>
+      </c>
+      <c r="D20">
+        <v>1.7018230000000001</v>
+      </c>
+      <c r="E20">
+        <v>7.0630740000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>64</v>
+      </c>
+      <c r="B21">
+        <v>0.175349</v>
+      </c>
+      <c r="C21">
+        <v>4.7182089999999999</v>
+      </c>
+      <c r="D21">
+        <v>1.561496</v>
+      </c>
+      <c r="E21">
+        <v>7.0868510000000002</v>
       </c>
     </row>
   </sheetData>

--- a/RunningTimeRecord.xlsx
+++ b/RunningTimeRecord.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62499079-4B7C-42CF-B560-9A89B60CE0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77804A69-578B-4204-8A6F-CD8C52ABBA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="13">
   <si>
     <t>n</t>
   </si>
@@ -71,6 +71,12 @@
   <si>
     <t>POSIX (Dynamic Pool Task)</t>
   </si>
+  <si>
+    <t>Speedup</t>
+  </si>
+  <si>
+    <t>Serial Code (Baseline)</t>
+  </si>
 </sst>
 </file>
 
@@ -85,7 +91,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -94,24 +100,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -119,26 +113,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -150,19 +129,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -443,20 +431,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="7" width="22.6640625" customWidth="1"/>
+    <col min="1" max="8" width="22.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -465,12 +453,13 @@
         <v>9</v>
       </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="9"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -487,13 +476,16 @@
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>10000000</v>
       </c>
@@ -511,13 +503,17 @@
         <v>4.681508</v>
       </c>
       <c r="F5">
+        <f>B5/D5</f>
+        <v>6.058049586295728</v>
+      </c>
+      <c r="G5" s="11">
         <v>1.446939</v>
       </c>
-      <c r="G5">
+      <c r="H5" s="11">
         <v>6.7915789999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>15000000</v>
       </c>
@@ -535,13 +531,17 @@
         <v>7.507098</v>
       </c>
       <c r="F6">
+        <f t="shared" ref="F6:F13" si="0">B6/D6</f>
+        <v>6.5393466683584061</v>
+      </c>
+      <c r="G6" s="11">
         <v>2.2352059999999998</v>
       </c>
-      <c r="G6">
+      <c r="H6" s="11">
         <v>9.9260079999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>20000000</v>
       </c>
@@ -559,13 +559,17 @@
         <v>10.757872000000001</v>
       </c>
       <c r="F7">
+        <f t="shared" si="0"/>
+        <v>6.6328130931887905</v>
+      </c>
+      <c r="G7" s="11">
         <v>2.9332560000000001</v>
       </c>
-      <c r="G7">
+      <c r="H7" s="11">
         <v>13.217007000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>25000000</v>
       </c>
@@ -583,13 +587,17 @@
         <v>13.035807999999999</v>
       </c>
       <c r="F8">
+        <f t="shared" si="0"/>
+        <v>6.7026539561422931</v>
+      </c>
+      <c r="G8" s="11">
         <v>3.5631789999999999</v>
       </c>
-      <c r="G8">
+      <c r="H8" s="11">
         <v>16.510265</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>30000000</v>
       </c>
@@ -607,13 +615,17 @@
         <v>15.552023999999999</v>
       </c>
       <c r="F9">
+        <f t="shared" si="0"/>
+        <v>6.7533383039616393</v>
+      </c>
+      <c r="G9" s="11">
         <v>4.2926489999999999</v>
       </c>
-      <c r="G9">
+      <c r="H9" s="11">
         <v>19.987759</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>35000000</v>
       </c>
@@ -631,13 +643,17 @@
         <v>18.931266000000001</v>
       </c>
       <c r="F10">
+        <f t="shared" si="0"/>
+        <v>6.7369673963036618</v>
+      </c>
+      <c r="G10" s="11">
         <v>5.0395729999999999</v>
       </c>
-      <c r="G10">
+      <c r="H10" s="11">
         <v>23.276264000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>40000000</v>
       </c>
@@ -655,13 +671,17 @@
         <v>25.360261000000001</v>
       </c>
       <c r="F11">
+        <f t="shared" si="0"/>
+        <v>7.0110466600395709</v>
+      </c>
+      <c r="G11" s="11">
         <v>5.6888629999999996</v>
       </c>
-      <c r="G11">
+      <c r="H11" s="11">
         <v>25.529710000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>45000000</v>
       </c>
@@ -679,13 +699,17 @@
         <v>28.095462000000001</v>
       </c>
       <c r="F12">
+        <f t="shared" si="0"/>
+        <v>7.0309831631451454</v>
+      </c>
+      <c r="G12" s="11">
         <v>6.5045169999999999</v>
       </c>
-      <c r="G12">
+      <c r="H12" s="11">
         <v>29.8569</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>50000000</v>
       </c>
@@ -703,21 +727,24 @@
         <v>31.271104000000001</v>
       </c>
       <c r="F13">
+        <f t="shared" si="0"/>
+        <v>7.4723465002555303</v>
+      </c>
+      <c r="G13" s="11">
         <v>7.2976419999999997</v>
       </c>
-      <c r="G13">
+      <c r="H13" s="11">
         <v>35.428055000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
+    <row r="16" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
@@ -726,213 +753,199 @@
         <v>9</v>
       </c>
       <c r="E16" s="6"/>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="6"/>
+      <c r="G16" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="H17" s="13" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11">
+    <row r="18" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
         <v>10000000</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12">
+      <c r="D18" s="5">
         <v>0.188636</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="5">
         <v>4.9392230000000001</v>
       </c>
-      <c r="F18" s="12">
+      <c r="G18" s="14">
         <v>1.384317</v>
       </c>
-      <c r="G18" s="12">
+      <c r="H18" s="14">
         <v>6.1650879999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+    <row r="19" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
         <v>15000000</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
       <c r="D19" s="5">
         <v>0.30043999999999998</v>
       </c>
       <c r="E19" s="5">
         <v>8.0359610000000004</v>
       </c>
-      <c r="F19" s="5">
+      <c r="G19" s="14">
         <v>2.5880679999999998</v>
       </c>
-      <c r="G19" s="5">
+      <c r="H19" s="14">
         <v>10.625273</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11">
+    <row r="20" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
         <v>20000000</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12">
+      <c r="D20" s="5">
         <v>0.446938</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="5">
         <v>10.283652</v>
       </c>
-      <c r="F20" s="12">
+      <c r="G20" s="14">
         <v>2.7769949999999999</v>
       </c>
-      <c r="G20" s="12">
+      <c r="H20" s="14">
         <v>12.613759999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+    <row r="21" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
         <v>25000000</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
       <c r="D21" s="5">
         <v>0.60850400000000004</v>
       </c>
       <c r="E21" s="5">
         <v>11.7872</v>
       </c>
-      <c r="F21" s="5">
+      <c r="G21" s="14">
         <v>3.9838559999999998</v>
       </c>
-      <c r="G21" s="5">
+      <c r="H21" s="14">
         <v>16.541592000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11">
+    <row r="22" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
         <v>30000000</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12">
+      <c r="D22" s="5">
         <v>0.78666400000000003</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="5">
         <v>16.037421999999999</v>
       </c>
-      <c r="F22" s="12">
+      <c r="G22" s="14">
         <v>5.5545479999999996</v>
       </c>
-      <c r="G22" s="12">
+      <c r="H22" s="14">
         <v>19.275448000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+    <row r="23" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8">
         <v>35000000</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
       <c r="D23" s="5">
         <v>0.97917200000000004</v>
       </c>
       <c r="E23" s="5">
         <v>16.859352000000001</v>
       </c>
-      <c r="F23" s="5">
+      <c r="G23" s="14">
         <v>6.1012940000000002</v>
       </c>
-      <c r="G23" s="5">
+      <c r="H23" s="14">
         <v>22.961316</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11">
+    <row r="24" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
         <v>40000000</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12">
+      <c r="D24" s="5">
         <v>1.135345</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="5">
         <v>22.491413999999999</v>
       </c>
-      <c r="F24" s="12">
+      <c r="G24" s="14">
         <v>6.5744150000000001</v>
       </c>
-      <c r="G24" s="12">
+      <c r="H24" s="14">
         <v>25.531298</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
+    <row r="25" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
         <v>45000000</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
       <c r="D25" s="5">
         <v>1.3597349999999999</v>
       </c>
       <c r="E25" s="5">
         <v>24.880361000000001</v>
       </c>
-      <c r="F25" s="5">
+      <c r="G25" s="14">
         <v>7.7472500000000002</v>
       </c>
-      <c r="G25" s="5">
+      <c r="H25" s="14">
         <v>31.823687</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11">
+    <row r="26" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
         <v>50000000</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12">
+      <c r="D26" s="5">
         <v>1.552114</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="5">
         <v>25.495045000000001</v>
       </c>
-      <c r="F26" s="12">
+      <c r="G26" s="14">
         <v>9.0593489999999992</v>
       </c>
-      <c r="G26" s="12">
+      <c r="H26" s="14">
         <v>31.419589999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G16:H16"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D16:F16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -940,30 +953,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2B590C-628F-42C3-BA14-2549B4CA5D44}">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="22.6640625" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="5" width="22.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="4" t="s">
+      <c r="B1" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,136 +989,190 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5">
+        <v>4.1623950000000001</v>
+      </c>
+      <c r="C5">
         <v>1.9988060000000001</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>7.4344469999999996</v>
       </c>
-      <c r="D5">
+      <c r="E5">
+        <f>B5/C5</f>
+        <v>2.0824407171081134</v>
+      </c>
+      <c r="F5" s="11">
         <v>2.1946720000000002</v>
       </c>
-      <c r="E5">
+      <c r="G5" s="11">
         <v>7.352087</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
+        <v>4.1623950000000001</v>
+      </c>
+      <c r="C6">
         <v>1.163114</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>6.4049259999999997</v>
       </c>
-      <c r="D6">
+      <c r="E6">
+        <f t="shared" ref="E6:E10" si="0">B6/C6</f>
+        <v>3.5786646880701292</v>
+      </c>
+      <c r="F6" s="11">
         <v>1.1574359999999999</v>
       </c>
-      <c r="E6">
+      <c r="G6" s="11">
         <v>6.3732189999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>8</v>
       </c>
       <c r="B7">
+        <v>4.1623950000000001</v>
+      </c>
+      <c r="C7">
         <v>0.66360600000000003</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>6.0478170000000002</v>
       </c>
-      <c r="D7">
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>6.272389038073797</v>
+      </c>
+      <c r="F7" s="11">
         <v>1.4256819999999999</v>
       </c>
-      <c r="E7">
+      <c r="G7" s="11">
         <v>6.6873300000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>16</v>
       </c>
       <c r="B8">
+        <v>4.1623950000000001</v>
+      </c>
+      <c r="C8">
         <v>0.445718</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>5.636774</v>
       </c>
-      <c r="D8">
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>9.3386289088616579</v>
+      </c>
+      <c r="F8" s="11">
         <v>1.4419729999999999</v>
       </c>
-      <c r="E8">
+      <c r="G8" s="11">
         <v>6.7687369999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>32</v>
       </c>
       <c r="B9">
+        <v>4.1623950000000001</v>
+      </c>
+      <c r="C9">
         <v>0.44677899999999998</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>5.6503730000000001</v>
       </c>
-      <c r="D9">
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>9.3164517580280197</v>
+      </c>
+      <c r="F9" s="11">
         <v>1.43801</v>
       </c>
-      <c r="E9">
+      <c r="G9" s="11">
         <v>7.2332419999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>64</v>
       </c>
       <c r="B10">
+        <v>4.1623950000000001</v>
+      </c>
+      <c r="C10">
         <v>0.44517200000000001</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>5.6201809999999996</v>
       </c>
-      <c r="D10">
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>9.350082664677922</v>
+      </c>
+      <c r="F10" s="11">
         <v>1.439022</v>
       </c>
-      <c r="E10">
+      <c r="G10" s="11">
         <v>6.5813569999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="4" t="s">
+      <c r="B12" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1108,123 +1180,129 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="G15" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16">
+      <c r="C16">
         <v>1.7803150000000001</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>7.0986909999999996</v>
       </c>
-      <c r="D16">
+      <c r="F16" s="11">
         <v>1.540073</v>
       </c>
-      <c r="E16">
+      <c r="G16" s="11">
         <v>6.6633519999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>4</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>0.91214399999999995</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>5.3931120000000004</v>
       </c>
-      <c r="D17">
+      <c r="F17" s="11">
         <v>1.2319119999999999</v>
       </c>
-      <c r="E17">
+      <c r="G17" s="11">
         <v>6.6738819999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>8</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>0.41222500000000001</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>5.5883979999999998</v>
       </c>
-      <c r="D18">
+      <c r="F18" s="11">
         <v>1.4754229999999999</v>
       </c>
-      <c r="E18">
+      <c r="G18" s="11">
         <v>6.1407610000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19">
+      <c r="C19">
         <v>0.248222</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>5.4797409999999998</v>
       </c>
-      <c r="D19">
+      <c r="F19" s="11">
         <v>1.988049</v>
       </c>
-      <c r="E19">
+      <c r="G19" s="11">
         <v>7.3005849999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>32</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>0.18618000000000001</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>4.9896700000000003</v>
       </c>
-      <c r="D20">
+      <c r="F20" s="11">
         <v>1.7018230000000001</v>
       </c>
-      <c r="E20">
+      <c r="G20" s="11">
         <v>7.0630740000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>64</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>0.175349</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>4.7182089999999999</v>
       </c>
-      <c r="D21">
+      <c r="F21" s="11">
         <v>1.561496</v>
       </c>
-      <c r="E21">
+      <c r="G21" s="11">
         <v>7.0868510000000002</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/RunningTimeRecord.xlsx
+++ b/RunningTimeRecord.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62499079-4B7C-42CF-B560-9A89B60CE0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4B2AED-CA77-417B-9CBF-A83EF2921DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -147,13 +147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -163,6 +157,12 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,18 +457,18 @@
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -716,212 +716,248 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6" t="s">
+    <row r="16" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6" t="s">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6" t="s">
+      <c r="E16" s="13"/>
+      <c r="F16" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="G16" s="13"/>
+    </row>
+    <row r="17" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11">
+    <row r="18" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9">
         <v>10000000</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12">
+      <c r="B18" s="10">
+        <v>3.778915</v>
+      </c>
+      <c r="C18" s="10">
+        <v>8.6425140000000003</v>
+      </c>
+      <c r="D18" s="10">
         <v>0.188636</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="10">
         <v>4.9392230000000001</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="10">
         <v>1.384317</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="10">
         <v>6.1650879999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+    <row r="19" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
         <v>15000000</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5">
+      <c r="B19" s="4">
+        <v>6.2206219999999997</v>
+      </c>
+      <c r="C19" s="4">
+        <v>13.401472999999999</v>
+      </c>
+      <c r="D19" s="4">
         <v>0.30043999999999998</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>8.0359610000000004</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
         <v>2.5880679999999998</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <v>10.625273</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11">
+    <row r="20" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9">
         <v>20000000</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12">
+      <c r="B20" s="10">
+        <v>10.102762</v>
+      </c>
+      <c r="C20" s="10">
+        <v>19.441248000000002</v>
+      </c>
+      <c r="D20" s="10">
         <v>0.446938</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="10">
         <v>10.283652</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="10">
         <v>2.7769949999999999</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="10">
         <v>12.613759999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+    <row r="21" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
         <v>25000000</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5">
+      <c r="B21" s="4">
+        <v>13.203678</v>
+      </c>
+      <c r="C21" s="4">
+        <v>25.747924000000001</v>
+      </c>
+      <c r="D21" s="4">
         <v>0.60850400000000004</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>11.7872</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="4">
         <v>3.9838559999999998</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="4">
         <v>16.541592000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11">
+    <row r="22" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9">
         <v>30000000</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12">
+      <c r="B22" s="10">
+        <v>17.911546000000001</v>
+      </c>
+      <c r="C22" s="10">
+        <v>30.626833000000001</v>
+      </c>
+      <c r="D22" s="10">
         <v>0.78666400000000003</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="10">
         <v>16.037421999999999</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="10">
         <v>5.5545479999999996</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="10">
         <v>19.275448000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+    <row r="23" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
         <v>35000000</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5">
+      <c r="B23" s="4">
+        <v>19.685684999999999</v>
+      </c>
+      <c r="C23" s="4">
+        <v>35.967072999999999</v>
+      </c>
+      <c r="D23" s="4">
         <v>0.97917200000000004</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <v>16.859352000000001</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="4">
         <v>6.1012940000000002</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="4">
         <v>22.961316</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11">
+    <row r="24" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9">
         <v>40000000</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12">
+      <c r="B24" s="10">
+        <v>26.964960999999999</v>
+      </c>
+      <c r="C24" s="10">
+        <v>47.716700000000003</v>
+      </c>
+      <c r="D24" s="10">
         <v>1.135345</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="10">
         <v>22.491413999999999</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="10">
         <v>6.5744150000000001</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="10">
         <v>25.531298</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
+    <row r="25" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
         <v>45000000</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5">
+      <c r="B25" s="4">
+        <v>31.982582000000001</v>
+      </c>
+      <c r="C25" s="4">
+        <v>55.762712000000001</v>
+      </c>
+      <c r="D25" s="4">
         <v>1.3597349999999999</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>24.880361000000001</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="4">
         <v>7.7472500000000002</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="4">
         <v>31.823687</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11">
+    <row r="26" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9">
         <v>50000000</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12">
+      <c r="B26" s="10">
+        <v>33.868523000000003</v>
+      </c>
+      <c r="C26" s="10">
+        <v>57.504927000000002</v>
+      </c>
+      <c r="D26" s="10">
         <v>1.552114</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="10">
         <v>25.495045000000001</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="10">
         <v>9.0593489999999992</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="10">
         <v>31.419589999999999</v>
       </c>
     </row>
@@ -954,14 +990,14 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="12"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1091,14 +1127,14 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4" t="s">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="12"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">

--- a/RunningTimeRecord.xlsx
+++ b/RunningTimeRecord.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77804A69-578B-4204-8A6F-CD8C52ABBA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBB60A7-49C7-4CBF-98A7-5BD253E40718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -126,31 +126,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,19 +430,19 @@
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="9" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="9"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -478,10 +463,10 @@
       <c r="F4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -506,10 +491,10 @@
         <f>B5/D5</f>
         <v>6.058049586295728</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="5">
         <v>1.446939</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="5">
         <v>6.7915789999999996</v>
       </c>
     </row>
@@ -534,10 +519,10 @@
         <f t="shared" ref="F6:F13" si="0">B6/D6</f>
         <v>6.5393466683584061</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="5">
         <v>2.2352059999999998</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="5">
         <v>9.9260079999999995</v>
       </c>
     </row>
@@ -562,10 +547,10 @@
         <f t="shared" si="0"/>
         <v>6.6328130931887905</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="5">
         <v>2.9332560000000001</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="5">
         <v>13.217007000000001</v>
       </c>
     </row>
@@ -590,10 +575,10 @@
         <f t="shared" si="0"/>
         <v>6.7026539561422931</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="5">
         <v>3.5631789999999999</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="5">
         <v>16.510265</v>
       </c>
     </row>
@@ -618,10 +603,10 @@
         <f t="shared" si="0"/>
         <v>6.7533383039616393</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="5">
         <v>4.2926489999999999</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="5">
         <v>19.987759</v>
       </c>
     </row>
@@ -646,10 +631,10 @@
         <f t="shared" si="0"/>
         <v>6.7369673963036618</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="5">
         <v>5.0395729999999999</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="5">
         <v>23.276264000000001</v>
       </c>
     </row>
@@ -674,10 +659,10 @@
         <f t="shared" si="0"/>
         <v>7.0110466600395709</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="5">
         <v>5.6888629999999996</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="5">
         <v>25.529710000000001</v>
       </c>
     </row>
@@ -702,10 +687,10 @@
         <f t="shared" si="0"/>
         <v>7.0309831631451454</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="5">
         <v>6.5045169999999999</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="5">
         <v>29.8569</v>
       </c>
     </row>
@@ -730,10 +715,10 @@
         <f t="shared" si="0"/>
         <v>7.4723465002555303</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="5">
         <v>7.2976419999999997</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="5">
         <v>35.428055000000001</v>
       </c>
     </row>
@@ -744,197 +729,287 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="6" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6" t="s">
+      <c r="C16" s="7"/>
+      <c r="D16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="12" t="s">
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="H17" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>10000000</v>
       </c>
-      <c r="D18" s="5">
+      <c r="B18">
+        <v>3.778915</v>
+      </c>
+      <c r="C18">
+        <v>8.6425140000000003</v>
+      </c>
+      <c r="D18">
         <v>0.188636</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18">
         <v>4.9392230000000001</v>
       </c>
-      <c r="G18" s="14">
+      <c r="F18">
+        <f>B18/D18</f>
+        <v>20.032841027163425</v>
+      </c>
+      <c r="G18" s="5">
         <v>1.384317</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="5">
         <v>6.1650879999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>15000000</v>
       </c>
-      <c r="D19" s="5">
+      <c r="B19">
+        <v>6.2206219999999997</v>
+      </c>
+      <c r="C19">
+        <v>13.401472999999999</v>
+      </c>
+      <c r="D19">
         <v>0.30043999999999998</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19">
         <v>8.0359610000000004</v>
       </c>
-      <c r="G19" s="14">
+      <c r="F19">
+        <f t="shared" ref="F19:F26" si="1">B19/D19</f>
+        <v>20.705039275728932</v>
+      </c>
+      <c r="G19" s="5">
         <v>2.5880679999999998</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="5">
         <v>10.625273</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>20000000</v>
       </c>
-      <c r="D20" s="5">
+      <c r="B20">
+        <v>10.102762</v>
+      </c>
+      <c r="C20">
+        <v>19.441248000000002</v>
+      </c>
+      <c r="D20">
         <v>0.446938</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20">
         <v>10.283652</v>
       </c>
-      <c r="G20" s="14">
+      <c r="F20">
+        <f t="shared" si="1"/>
+        <v>22.604392555566992</v>
+      </c>
+      <c r="G20" s="5">
         <v>2.7769949999999999</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="5">
         <v>12.613759999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>25000000</v>
       </c>
-      <c r="D21" s="5">
+      <c r="B21">
+        <v>13.203678</v>
+      </c>
+      <c r="C21">
+        <v>25.747924000000001</v>
+      </c>
+      <c r="D21">
         <v>0.60850400000000004</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21">
         <v>11.7872</v>
       </c>
-      <c r="G21" s="14">
+      <c r="F21">
+        <f t="shared" si="1"/>
+        <v>21.698588669918355</v>
+      </c>
+      <c r="G21" s="5">
         <v>3.9838559999999998</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="5">
         <v>16.541592000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>30000000</v>
       </c>
-      <c r="D22" s="5">
+      <c r="B22">
+        <v>17.911546000000001</v>
+      </c>
+      <c r="C22">
+        <v>30.626833000000001</v>
+      </c>
+      <c r="D22">
         <v>0.78666400000000003</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22">
         <v>16.037421999999999</v>
       </c>
-      <c r="G22" s="14">
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>22.768991589801999</v>
+      </c>
+      <c r="G22" s="5">
         <v>5.5545479999999996</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="5">
         <v>19.275448000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>35000000</v>
       </c>
-      <c r="D23" s="5">
+      <c r="B23">
+        <v>19.685684999999999</v>
+      </c>
+      <c r="C23">
+        <v>35.967072999999999</v>
+      </c>
+      <c r="D23">
         <v>0.97917200000000004</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23">
         <v>16.859352000000001</v>
       </c>
-      <c r="G23" s="14">
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>20.10441985677695</v>
+      </c>
+      <c r="G23" s="5">
         <v>6.1012940000000002</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="5">
         <v>22.961316</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>40000000</v>
       </c>
-      <c r="D24" s="5">
+      <c r="B24">
+        <v>26.964960999999999</v>
+      </c>
+      <c r="C24">
+        <v>47.716700000000003</v>
+      </c>
+      <c r="D24">
         <v>1.135345</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24">
         <v>22.491413999999999</v>
       </c>
-      <c r="G24" s="14">
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>23.750455588389432</v>
+      </c>
+      <c r="G24" s="5">
         <v>6.5744150000000001</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="5">
         <v>25.531298</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>45000000</v>
       </c>
-      <c r="D25" s="5">
+      <c r="B25">
+        <v>31.982582000000001</v>
+      </c>
+      <c r="C25">
+        <v>55.762712000000001</v>
+      </c>
+      <c r="D25">
         <v>1.3597349999999999</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25">
         <v>24.880361000000001</v>
       </c>
-      <c r="G25" s="14">
+      <c r="F25">
+        <f t="shared" si="1"/>
+        <v>23.52118758434548</v>
+      </c>
+      <c r="G25" s="5">
         <v>7.7472500000000002</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="5">
         <v>31.823687</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>50000000</v>
       </c>
-      <c r="D26" s="5">
+      <c r="B26">
+        <v>33.868523000000003</v>
+      </c>
+      <c r="C26">
+        <v>57.504927000000002</v>
+      </c>
+      <c r="D26">
         <v>1.552114</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26">
         <v>25.495045000000001</v>
       </c>
-      <c r="G26" s="14">
+      <c r="F26">
+        <f t="shared" si="1"/>
+        <v>21.820899109214917</v>
+      </c>
+      <c r="G26" s="5">
         <v>9.0593489999999992</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="5">
         <v>31.419589999999999</v>
       </c>
     </row>
@@ -971,15 +1046,15 @@
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="9" t="s">
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="9"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -997,10 +1072,10 @@
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1021,10 +1096,10 @@
         <f>B5/C5</f>
         <v>2.0824407171081134</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="5">
         <v>2.1946720000000002</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="5">
         <v>7.352087</v>
       </c>
     </row>
@@ -1045,10 +1120,10 @@
         <f t="shared" ref="E6:E10" si="0">B6/C6</f>
         <v>3.5786646880701292</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="5">
         <v>1.1574359999999999</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="5">
         <v>6.3732189999999997</v>
       </c>
     </row>
@@ -1069,10 +1144,10 @@
         <f t="shared" si="0"/>
         <v>6.272389038073797</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="5">
         <v>1.4256819999999999</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="5">
         <v>6.6873300000000002</v>
       </c>
     </row>
@@ -1093,10 +1168,10 @@
         <f t="shared" si="0"/>
         <v>9.3386289088616579</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="5">
         <v>1.4419729999999999</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="5">
         <v>6.7687369999999998</v>
       </c>
     </row>
@@ -1117,10 +1192,10 @@
         <f t="shared" si="0"/>
         <v>9.3164517580280197</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="5">
         <v>1.43801</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="5">
         <v>7.2332419999999997</v>
       </c>
     </row>
@@ -1141,10 +1216,10 @@
         <f t="shared" si="0"/>
         <v>9.350082664677922</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="5">
         <v>1.439022</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="5">
         <v>6.5813569999999997</v>
       </c>
     </row>
@@ -1162,15 +1237,15 @@
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="9" t="s">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="9"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
@@ -1188,10 +1263,10 @@
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1199,16 +1274,23 @@
       <c r="A16">
         <v>1</v>
       </c>
+      <c r="B16">
+        <v>3.778915</v>
+      </c>
       <c r="C16">
         <v>1.7803150000000001</v>
       </c>
       <c r="D16">
         <v>7.0986909999999996</v>
       </c>
-      <c r="F16" s="11">
+      <c r="E16">
+        <f>B16/C16</f>
+        <v>2.122610324577392</v>
+      </c>
+      <c r="F16" s="5">
         <v>1.540073</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="5">
         <v>6.6633519999999997</v>
       </c>
     </row>
@@ -1216,16 +1298,23 @@
       <c r="A17">
         <v>4</v>
       </c>
+      <c r="B17">
+        <v>3.778915</v>
+      </c>
       <c r="C17">
         <v>0.91214399999999995</v>
       </c>
       <c r="D17">
         <v>5.3931120000000004</v>
       </c>
-      <c r="F17" s="11">
+      <c r="E17">
+        <f t="shared" ref="E17:E21" si="1">B17/C17</f>
+        <v>4.1428930081215247</v>
+      </c>
+      <c r="F17" s="5">
         <v>1.2319119999999999</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="5">
         <v>6.6738819999999999</v>
       </c>
     </row>
@@ -1233,16 +1322,23 @@
       <c r="A18">
         <v>8</v>
       </c>
+      <c r="B18">
+        <v>3.778915</v>
+      </c>
       <c r="C18">
         <v>0.41222500000000001</v>
       </c>
       <c r="D18">
         <v>5.5883979999999998</v>
       </c>
-      <c r="F18" s="11">
+      <c r="E18">
+        <f t="shared" si="1"/>
+        <v>9.1671174722542297</v>
+      </c>
+      <c r="F18" s="5">
         <v>1.4754229999999999</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="5">
         <v>6.1407610000000004</v>
       </c>
     </row>
@@ -1250,16 +1346,23 @@
       <c r="A19">
         <v>16</v>
       </c>
+      <c r="B19">
+        <v>3.778915</v>
+      </c>
       <c r="C19">
         <v>0.248222</v>
       </c>
       <c r="D19">
         <v>5.4797409999999998</v>
       </c>
-      <c r="F19" s="11">
+      <c r="E19">
+        <f t="shared" si="1"/>
+        <v>15.223932608713168</v>
+      </c>
+      <c r="F19" s="5">
         <v>1.988049</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="5">
         <v>7.3005849999999999</v>
       </c>
     </row>
@@ -1267,16 +1370,23 @@
       <c r="A20">
         <v>32</v>
       </c>
+      <c r="B20">
+        <v>3.778915</v>
+      </c>
       <c r="C20">
         <v>0.18618000000000001</v>
       </c>
       <c r="D20">
         <v>4.9896700000000003</v>
       </c>
-      <c r="F20" s="11">
+      <c r="E20">
+        <f t="shared" si="1"/>
+        <v>20.297104952196797</v>
+      </c>
+      <c r="F20" s="5">
         <v>1.7018230000000001</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="5">
         <v>7.0630740000000003</v>
       </c>
     </row>
@@ -1284,16 +1394,23 @@
       <c r="A21">
         <v>64</v>
       </c>
+      <c r="B21">
+        <v>3.778915</v>
+      </c>
       <c r="C21">
         <v>0.175349</v>
       </c>
       <c r="D21">
         <v>4.7182089999999999</v>
       </c>
-      <c r="F21" s="11">
+      <c r="E21">
+        <f t="shared" si="1"/>
+        <v>21.55082150454237</v>
+      </c>
+      <c r="F21" s="5">
         <v>1.561496</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="5">
         <v>7.0868510000000002</v>
       </c>
     </row>

--- a/RunningTimeRecord.xlsx
+++ b/RunningTimeRecord.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBB60A7-49C7-4CBF-98A7-5BD253E40718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>

--- a/RunningTimeRecord.xlsx
+++ b/RunningTimeRecord.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBB60A7-49C7-4CBF-98A7-5BD253E40718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6E0418-6ABA-4BA1-80CB-AD25423B853B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
   <si>
     <t>n</t>
   </si>
@@ -91,7 +91,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -101,6 +101,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -117,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -130,10 +136,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -416,611 +426,902 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="8" width="22.6328125" customWidth="1"/>
+    <col min="1" max="6" width="22.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B3" s="7" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>10000000</v>
       </c>
       <c r="B5">
-        <v>4.1623950000000001</v>
-      </c>
-      <c r="C5">
-        <f>5.247637+B5</f>
-        <v>9.4100320000000011</v>
-      </c>
+        <v>4.221819</v>
+      </c>
+      <c r="C5" s="7"/>
       <c r="D5">
-        <v>0.68708499999999995</v>
-      </c>
-      <c r="E5">
-        <v>4.681508</v>
-      </c>
+        <v>0.66401900000000003</v>
+      </c>
+      <c r="E5" s="7"/>
       <c r="F5">
         <f>B5/D5</f>
-        <v>6.058049586295728</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1.446939</v>
-      </c>
-      <c r="H5" s="5">
-        <v>6.7915789999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>6.3579792144501885</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
+        <v>11000000</v>
+      </c>
+      <c r="B6">
+        <v>4.7456699999999996</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6">
+        <v>0.76085100000000006</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6">
+        <f t="shared" ref="F6:F35" si="0">B6/D6</f>
+        <v>6.2373184762851057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="B7">
+        <v>5.4632949999999996</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7">
+        <v>0.84793499999999999</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>6.4430587250201956</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>13000000</v>
+      </c>
+      <c r="B8">
+        <v>6.0686730000000004</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8">
+        <v>0.93635000000000002</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>6.4812014738078716</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>14000000</v>
+      </c>
+      <c r="B9">
+        <v>6.7864820000000003</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9">
+        <v>1.0725750000000001</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>6.3272796774118358</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>15000000</v>
       </c>
-      <c r="B6">
-        <v>7.627834</v>
-      </c>
-      <c r="C6">
-        <f>8.309336+B6</f>
-        <v>15.93717</v>
-      </c>
-      <c r="D6">
-        <v>1.166452</v>
-      </c>
-      <c r="E6">
-        <v>7.507098</v>
-      </c>
-      <c r="F6">
-        <f t="shared" ref="F6:F13" si="0">B6/D6</f>
-        <v>6.5393466683584061</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2.2352059999999998</v>
-      </c>
-      <c r="H6" s="5">
-        <v>9.9260079999999995</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+      <c r="B10">
+        <v>7.5130920000000003</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10">
+        <v>1.16066</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>6.4731204659417916</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="B11">
+        <v>8.2434170000000009</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11">
+        <v>1.268275</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>6.4997078709270468</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>17000000</v>
+      </c>
+      <c r="B12">
+        <v>9.0389809999999997</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12">
+        <v>1.3796630000000001</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>6.5515861482115554</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="B13">
+        <v>11.076497</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13">
+        <v>1.566074</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>7.0727800857430747</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="B14">
+        <v>11.668153999999999</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14">
+        <v>1.6360399999999999</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>7.1319490965991053</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>20000000</v>
       </c>
-      <c r="B7">
-        <v>11.705761000000001</v>
-      </c>
-      <c r="C7">
-        <f>10.886813+B7</f>
-        <v>22.592573999999999</v>
-      </c>
-      <c r="D7">
-        <v>1.764826</v>
-      </c>
-      <c r="E7">
-        <v>10.757872000000001</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
-        <v>6.6328130931887905</v>
-      </c>
-      <c r="G7" s="5">
-        <v>2.9332560000000001</v>
-      </c>
-      <c r="H7" s="5">
-        <v>13.217007000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+      <c r="B15">
+        <v>12.374013</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15">
+        <v>1.75071</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>7.0679969840807439</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>21000000</v>
+      </c>
+      <c r="B16">
+        <v>13.410712999999999</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16">
+        <v>1.9254990000000001</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>6.9647987352888778</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>22000000</v>
+      </c>
+      <c r="B17">
+        <v>13.503204</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17">
+        <v>2.0128330000000001</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>6.708556546916709</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>23000000</v>
+      </c>
+      <c r="B18">
+        <v>15.334875</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18">
+        <v>2.1030869999999999</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>7.2916027724958603</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>24000000</v>
+      </c>
+      <c r="B19">
+        <v>15.795399</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19">
+        <v>2.2671899999999998</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>6.9669498365818487</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>25000000</v>
       </c>
-      <c r="B8">
-        <v>15.923990999999999</v>
-      </c>
-      <c r="C8">
-        <f>12.898962+B8</f>
-        <v>28.822952999999998</v>
-      </c>
-      <c r="D8">
-        <v>2.3757739999999998</v>
-      </c>
-      <c r="E8">
-        <v>13.035807999999999</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="0"/>
-        <v>6.7026539561422931</v>
-      </c>
-      <c r="G8" s="5">
-        <v>3.5631789999999999</v>
-      </c>
-      <c r="H8" s="5">
-        <v>16.510265</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+      <c r="B20">
+        <v>17.032720999999999</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20">
+        <v>2.413516</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>7.0572231549324718</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>26000000</v>
+      </c>
+      <c r="B21">
+        <v>18.229096999999999</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21">
+        <v>2.524848</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>7.2198789788533801</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>27000000</v>
+      </c>
+      <c r="B22">
+        <v>19.070878</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22">
+        <v>2.716825</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>7.0195459773816866</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>28000000</v>
+      </c>
+      <c r="B23">
+        <v>20.289345000000001</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23">
+        <v>2.8388429999999998</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>7.1470472301567938</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>29000000</v>
+      </c>
+      <c r="B24">
+        <v>20.676687000000001</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24">
+        <v>2.9750390000000002</v>
+      </c>
+      <c r="E24" s="7"/>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>6.9500557807813612</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>30000000</v>
       </c>
-      <c r="B9">
-        <v>20.415963000000001</v>
-      </c>
-      <c r="C9">
-        <f>15.466003+B9</f>
-        <v>35.881966000000006</v>
-      </c>
-      <c r="D9">
-        <v>3.0230920000000001</v>
-      </c>
-      <c r="E9">
-        <v>15.552023999999999</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
-        <v>6.7533383039616393</v>
-      </c>
-      <c r="G9" s="5">
-        <v>4.2926489999999999</v>
-      </c>
-      <c r="H9" s="5">
-        <v>19.987759</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+      <c r="B25">
+        <v>21.899799999999999</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25">
+        <v>3.0683389999999999</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>7.1373469489518593</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>31000000</v>
+      </c>
+      <c r="B26">
+        <v>22.377856999999999</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26">
+        <v>3.2272479999999999</v>
+      </c>
+      <c r="E26" s="7"/>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>6.9340369875510026</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>32000000</v>
+      </c>
+      <c r="B27">
+        <v>24.132621</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27">
+        <v>3.381545</v>
+      </c>
+      <c r="E27" s="7"/>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>7.1365665694231479</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>33000000</v>
+      </c>
+      <c r="B28">
+        <v>24.831582999999998</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28">
+        <v>3.4923199999999999</v>
+      </c>
+      <c r="E28" s="7"/>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>7.1103401177440784</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>34000000</v>
+      </c>
+      <c r="B29">
+        <v>26.061553</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29">
+        <v>3.6668919999999998</v>
+      </c>
+      <c r="E29" s="7"/>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>7.1072594993253144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>35000000</v>
       </c>
-      <c r="B10">
-        <v>25.999472999999998</v>
-      </c>
-      <c r="C10">
-        <f>20.972771+B10</f>
-        <v>46.972244000000003</v>
-      </c>
-      <c r="D10">
-        <v>3.8592249999999999</v>
-      </c>
-      <c r="E10">
-        <v>18.931266000000001</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
-        <v>6.7369673963036618</v>
-      </c>
-      <c r="G10" s="5">
-        <v>5.0395729999999999</v>
-      </c>
-      <c r="H10" s="5">
-        <v>23.276264000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
+      <c r="B30">
+        <v>27.901105000000001</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30">
+        <v>3.7689819999999998</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>7.4028225658811859</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>36000000</v>
+      </c>
+      <c r="B31">
+        <v>28.604783999999999</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31">
+        <v>4.518008</v>
+      </c>
+      <c r="E31" s="7"/>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>6.3312822819260166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>37000000</v>
+      </c>
+      <c r="B32">
+        <v>29.860191</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32">
+        <v>5.2665649999999999</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>5.6697659670012621</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>38000000</v>
+      </c>
+      <c r="B33">
+        <v>30.595779</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33">
+        <v>4.8746859999999996</v>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>6.276461499263748</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
+        <v>39000000</v>
+      </c>
+      <c r="B34">
+        <v>30.810445000000001</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34">
+        <v>4.905627</v>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>6.2806334440021638</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
         <v>40000000</v>
       </c>
-      <c r="B11">
-        <v>32.189481999999998</v>
-      </c>
-      <c r="C11">
-        <f>25.823072+B11</f>
-        <v>58.012553999999994</v>
-      </c>
-      <c r="D11">
-        <v>4.5912519999999999</v>
-      </c>
-      <c r="E11">
-        <v>25.360261000000001</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>7.0110466600395709</v>
-      </c>
-      <c r="G11" s="5">
-        <v>5.6888629999999996</v>
-      </c>
-      <c r="H11" s="5">
-        <v>25.529710000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
-        <v>45000000</v>
-      </c>
-      <c r="B12">
-        <v>37.943916999999999</v>
-      </c>
-      <c r="C12">
-        <f>29.341272+B12</f>
-        <v>67.285189000000003</v>
-      </c>
-      <c r="D12">
-        <v>5.3966729999999998</v>
-      </c>
-      <c r="E12">
-        <v>28.095462000000001</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
-        <v>7.0309831631451454</v>
-      </c>
-      <c r="G12" s="5">
-        <v>6.5045169999999999</v>
-      </c>
-      <c r="H12" s="5">
-        <v>29.8569</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
-        <v>50000000</v>
-      </c>
-      <c r="B13">
-        <v>46.904995</v>
-      </c>
-      <c r="C13">
-        <f>31.02748+B13</f>
-        <v>77.932474999999997</v>
-      </c>
-      <c r="D13">
-        <v>6.2771439999999998</v>
-      </c>
-      <c r="E13">
-        <v>31.271104000000001</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
-        <v>7.4723465002555303</v>
-      </c>
-      <c r="G13" s="5">
-        <v>7.2976419999999997</v>
-      </c>
-      <c r="H13" s="5">
-        <v>35.428055000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+      <c r="B35">
+        <v>32.276363000000003</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35">
+        <v>5.2940889999999996</v>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>6.0966793342537322</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="7" t="s">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B38" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7" t="s">
+      <c r="C38" s="8"/>
+      <c r="D38" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C39" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E39" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F39" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>10000000</v>
       </c>
-      <c r="B18">
-        <v>3.778915</v>
-      </c>
-      <c r="C18">
-        <v>8.6425140000000003</v>
-      </c>
-      <c r="D18">
-        <v>0.188636</v>
-      </c>
-      <c r="E18">
-        <v>4.9392230000000001</v>
-      </c>
-      <c r="F18">
-        <f>B18/D18</f>
-        <v>20.032841027163425</v>
-      </c>
-      <c r="G18" s="5">
-        <v>1.384317</v>
-      </c>
-      <c r="H18" s="5">
-        <v>6.1650879999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+      <c r="C40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" t="e">
+        <f>B40/D40</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
+        <v>11000000</v>
+      </c>
+      <c r="F41" t="e">
+        <f t="shared" ref="F41:F70" si="1">B41/D41</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="F42" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
+        <v>13000000</v>
+      </c>
+      <c r="F43" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
+        <v>14000000</v>
+      </c>
+      <c r="F44" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
         <v>15000000</v>
       </c>
-      <c r="B19">
-        <v>6.2206219999999997</v>
-      </c>
-      <c r="C19">
-        <v>13.401472999999999</v>
-      </c>
-      <c r="D19">
-        <v>0.30043999999999998</v>
-      </c>
-      <c r="E19">
-        <v>8.0359610000000004</v>
-      </c>
-      <c r="F19">
-        <f t="shared" ref="F19:F26" si="1">B19/D19</f>
-        <v>20.705039275728932</v>
-      </c>
-      <c r="G19" s="5">
-        <v>2.5880679999999998</v>
-      </c>
-      <c r="H19" s="5">
-        <v>10.625273</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+      <c r="F45" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="F46" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
+        <v>17000000</v>
+      </c>
+      <c r="F47" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="F48" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="F49" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
         <v>20000000</v>
       </c>
-      <c r="B20">
-        <v>10.102762</v>
-      </c>
-      <c r="C20">
-        <v>19.441248000000002</v>
-      </c>
-      <c r="D20">
-        <v>0.446938</v>
-      </c>
-      <c r="E20">
-        <v>10.283652</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="1"/>
-        <v>22.604392555566992</v>
-      </c>
-      <c r="G20" s="5">
-        <v>2.7769949999999999</v>
-      </c>
-      <c r="H20" s="5">
-        <v>12.613759999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+      <c r="F50" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="2">
+        <v>21000000</v>
+      </c>
+      <c r="F51" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
+        <v>22000000</v>
+      </c>
+      <c r="F52" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="2">
+        <v>23000000</v>
+      </c>
+      <c r="F53" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
+        <v>24000000</v>
+      </c>
+      <c r="F54" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="2">
         <v>25000000</v>
       </c>
-      <c r="B21">
-        <v>13.203678</v>
-      </c>
-      <c r="C21">
-        <v>25.747924000000001</v>
-      </c>
-      <c r="D21">
-        <v>0.60850400000000004</v>
-      </c>
-      <c r="E21">
-        <v>11.7872</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="1"/>
-        <v>21.698588669918355</v>
-      </c>
-      <c r="G21" s="5">
-        <v>3.9838559999999998</v>
-      </c>
-      <c r="H21" s="5">
-        <v>16.541592000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+      <c r="F55" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
+        <v>26000000</v>
+      </c>
+      <c r="F56" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="2">
+        <v>27000000</v>
+      </c>
+      <c r="F57" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
+        <v>28000000</v>
+      </c>
+      <c r="F58" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="2">
+        <v>29000000</v>
+      </c>
+      <c r="F59" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
         <v>30000000</v>
       </c>
-      <c r="B22">
-        <v>17.911546000000001</v>
-      </c>
-      <c r="C22">
-        <v>30.626833000000001</v>
-      </c>
-      <c r="D22">
-        <v>0.78666400000000003</v>
-      </c>
-      <c r="E22">
-        <v>16.037421999999999</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="1"/>
-        <v>22.768991589801999</v>
-      </c>
-      <c r="G22" s="5">
-        <v>5.5545479999999996</v>
-      </c>
-      <c r="H22" s="5">
-        <v>19.275448000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
+      <c r="F60" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="2">
+        <v>31000000</v>
+      </c>
+      <c r="F61" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="2">
+        <v>32000000</v>
+      </c>
+      <c r="F62" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="2">
+        <v>33000000</v>
+      </c>
+      <c r="F63" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="2">
+        <v>34000000</v>
+      </c>
+      <c r="F64" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="2">
         <v>35000000</v>
       </c>
-      <c r="B23">
-        <v>19.685684999999999</v>
-      </c>
-      <c r="C23">
-        <v>35.967072999999999</v>
-      </c>
-      <c r="D23">
-        <v>0.97917200000000004</v>
-      </c>
-      <c r="E23">
-        <v>16.859352000000001</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>20.10441985677695</v>
-      </c>
-      <c r="G23" s="5">
-        <v>6.1012940000000002</v>
-      </c>
-      <c r="H23" s="5">
-        <v>22.961316</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+      <c r="F65" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
+        <v>36000000</v>
+      </c>
+      <c r="F66" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="2">
+        <v>37000000</v>
+      </c>
+      <c r="F67" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="2">
+        <v>38000000</v>
+      </c>
+      <c r="F68" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="2">
+        <v>39000000</v>
+      </c>
+      <c r="F69" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="2">
         <v>40000000</v>
       </c>
-      <c r="B24">
-        <v>26.964960999999999</v>
-      </c>
-      <c r="C24">
-        <v>47.716700000000003</v>
-      </c>
-      <c r="D24">
-        <v>1.135345</v>
-      </c>
-      <c r="E24">
-        <v>22.491413999999999</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="1"/>
-        <v>23.750455588389432</v>
-      </c>
-      <c r="G24" s="5">
-        <v>6.5744150000000001</v>
-      </c>
-      <c r="H24" s="5">
-        <v>25.531298</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
-        <v>45000000</v>
-      </c>
-      <c r="B25">
-        <v>31.982582000000001</v>
-      </c>
-      <c r="C25">
-        <v>55.762712000000001</v>
-      </c>
-      <c r="D25">
-        <v>1.3597349999999999</v>
-      </c>
-      <c r="E25">
-        <v>24.880361000000001</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="1"/>
-        <v>23.52118758434548</v>
-      </c>
-      <c r="G25" s="5">
-        <v>7.7472500000000002</v>
-      </c>
-      <c r="H25" s="5">
-        <v>31.823687</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
-        <v>50000000</v>
-      </c>
-      <c r="B26">
-        <v>33.868523000000003</v>
-      </c>
-      <c r="C26">
-        <v>57.504927000000002</v>
-      </c>
-      <c r="D26">
-        <v>1.552114</v>
-      </c>
-      <c r="E26">
-        <v>25.495045000000001</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="1"/>
-        <v>21.820899109214917</v>
-      </c>
-      <c r="G26" s="5">
-        <v>9.0593489999999992</v>
-      </c>
-      <c r="H26" s="5">
-        <v>31.419589999999999</v>
+      <c r="F70" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G16:H16"/>
+  <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="D3:F3"/>
-    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D38:F38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1046,15 +1347,15 @@
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="6" t="s">
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1237,15 +1538,15 @@
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="6" t="s">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="6"/>
+      <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">

--- a/RunningTimeRecord.xlsx
+++ b/RunningTimeRecord.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6E0418-6ABA-4BA1-80CB-AD25423B853B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622007D1-2C6F-483D-A3E3-DA6E9A12F7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
@@ -1385,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>4.1623950000000001</v>
+        <v>4.221819</v>
       </c>
       <c r="C5">
         <v>1.9988060000000001</v>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E5">
         <f>B5/C5</f>
-        <v>2.0824407171081134</v>
+        <v>2.1121704657680636</v>
       </c>
       <c r="F5" s="5">
         <v>2.1946720000000002</v>
@@ -1409,7 +1409,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>4.1623950000000001</v>
+        <v>4.221819</v>
       </c>
       <c r="C6">
         <v>1.163114</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E6">
         <f t="shared" ref="E6:E10" si="0">B6/C6</f>
-        <v>3.5786646880701292</v>
+        <v>3.6297551228856331</v>
       </c>
       <c r="F6" s="5">
         <v>1.1574359999999999</v>
@@ -1433,7 +1433,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>4.1623950000000001</v>
+        <v>4.221819</v>
       </c>
       <c r="C7">
         <v>0.66360600000000003</v>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>6.272389038073797</v>
+        <v>6.3619361488594128</v>
       </c>
       <c r="F7" s="5">
         <v>1.4256819999999999</v>
@@ -1457,7 +1457,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>4.1623950000000001</v>
+        <v>4.221819</v>
       </c>
       <c r="C8">
         <v>0.445718</v>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>9.3386289088616579</v>
+        <v>9.4719508747683516</v>
       </c>
       <c r="F8" s="5">
         <v>1.4419729999999999</v>
@@ -1481,7 +1481,7 @@
         <v>32</v>
       </c>
       <c r="B9">
-        <v>4.1623950000000001</v>
+        <v>4.221819</v>
       </c>
       <c r="C9">
         <v>0.44677899999999998</v>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>9.3164517580280197</v>
+        <v>9.4494571141436818</v>
       </c>
       <c r="F9" s="5">
         <v>1.43801</v>
@@ -1505,7 +1505,7 @@
         <v>64</v>
       </c>
       <c r="B10">
-        <v>4.1623950000000001</v>
+        <v>4.221819</v>
       </c>
       <c r="C10">
         <v>0.44517200000000001</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>9.350082664677922</v>
+        <v>9.4835681489401846</v>
       </c>
       <c r="F10" s="5">
         <v>1.439022</v>
@@ -1576,7 +1576,8 @@
         <v>1</v>
       </c>
       <c r="B16">
-        <v>3.778915</v>
+        <f>'Testing 1'!$B$40</f>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>1.7803150000000001</v>
@@ -1586,7 +1587,7 @@
       </c>
       <c r="E16">
         <f>B16/C16</f>
-        <v>2.122610324577392</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5">
         <v>1.540073</v>
@@ -1600,7 +1601,8 @@
         <v>4</v>
       </c>
       <c r="B17">
-        <v>3.778915</v>
+        <f>'Testing 1'!$B$40</f>
+        <v>0</v>
       </c>
       <c r="C17">
         <v>0.91214399999999995</v>
@@ -1610,7 +1612,7 @@
       </c>
       <c r="E17">
         <f t="shared" ref="E17:E21" si="1">B17/C17</f>
-        <v>4.1428930081215247</v>
+        <v>0</v>
       </c>
       <c r="F17" s="5">
         <v>1.2319119999999999</v>
@@ -1624,7 +1626,8 @@
         <v>8</v>
       </c>
       <c r="B18">
-        <v>3.778915</v>
+        <f>'Testing 1'!$B$40</f>
+        <v>0</v>
       </c>
       <c r="C18">
         <v>0.41222500000000001</v>
@@ -1634,7 +1637,7 @@
       </c>
       <c r="E18">
         <f t="shared" si="1"/>
-        <v>9.1671174722542297</v>
+        <v>0</v>
       </c>
       <c r="F18" s="5">
         <v>1.4754229999999999</v>
@@ -1648,7 +1651,8 @@
         <v>16</v>
       </c>
       <c r="B19">
-        <v>3.778915</v>
+        <f>'Testing 1'!$B$40</f>
+        <v>0</v>
       </c>
       <c r="C19">
         <v>0.248222</v>
@@ -1658,7 +1662,7 @@
       </c>
       <c r="E19">
         <f t="shared" si="1"/>
-        <v>15.223932608713168</v>
+        <v>0</v>
       </c>
       <c r="F19" s="5">
         <v>1.988049</v>
@@ -1672,7 +1676,8 @@
         <v>32</v>
       </c>
       <c r="B20">
-        <v>3.778915</v>
+        <f>'Testing 1'!$B$40</f>
+        <v>0</v>
       </c>
       <c r="C20">
         <v>0.18618000000000001</v>
@@ -1682,7 +1687,7 @@
       </c>
       <c r="E20">
         <f t="shared" si="1"/>
-        <v>20.297104952196797</v>
+        <v>0</v>
       </c>
       <c r="F20" s="5">
         <v>1.7018230000000001</v>
@@ -1696,7 +1701,8 @@
         <v>64</v>
       </c>
       <c r="B21">
-        <v>3.778915</v>
+        <f>'Testing 1'!$B$40</f>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>0.175349</v>
@@ -1706,7 +1712,7 @@
       </c>
       <c r="E21">
         <f t="shared" si="1"/>
-        <v>21.55082150454237</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5">
         <v>1.561496</v>

--- a/RunningTimeRecord.xlsx
+++ b/RunningTimeRecord.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622007D1-2C6F-483D-A3E3-DA6E9A12F7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD1F3FF-A27F-4FFC-A751-9FB56DBEEBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
@@ -427,19 +427,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="22.6328125" customWidth="1"/>
+    <col min="1" max="6" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
@@ -450,7 +450,7 @@
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -470,7 +470,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>10000000</v>
       </c>
@@ -487,7 +487,7 @@
         <v>6.3579792144501885</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>11000000</v>
       </c>
@@ -504,7 +504,7 @@
         <v>6.2373184762851057</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>12000000</v>
       </c>
@@ -521,7 +521,7 @@
         <v>6.4430587250201956</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>13000000</v>
       </c>
@@ -538,7 +538,7 @@
         <v>6.4812014738078716</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>14000000</v>
       </c>
@@ -555,7 +555,7 @@
         <v>6.3272796774118358</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>15000000</v>
       </c>
@@ -572,7 +572,7 @@
         <v>6.4731204659417916</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>16000000</v>
       </c>
@@ -589,7 +589,7 @@
         <v>6.4997078709270468</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>17000000</v>
       </c>
@@ -606,7 +606,7 @@
         <v>6.5515861482115554</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>18000000</v>
       </c>
@@ -623,7 +623,7 @@
         <v>7.0727800857430747</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>19000000</v>
       </c>
@@ -640,7 +640,7 @@
         <v>7.1319490965991053</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>20000000</v>
       </c>
@@ -657,7 +657,7 @@
         <v>7.0679969840807439</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>21000000</v>
       </c>
@@ -674,7 +674,7 @@
         <v>6.9647987352888778</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>22000000</v>
       </c>
@@ -691,7 +691,7 @@
         <v>6.708556546916709</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>23000000</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7.2916027724958603</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>24000000</v>
       </c>
@@ -725,7 +725,7 @@
         <v>6.9669498365818487</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>25000000</v>
       </c>
@@ -742,7 +742,7 @@
         <v>7.0572231549324718</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>26000000</v>
       </c>
@@ -759,7 +759,7 @@
         <v>7.2198789788533801</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>27000000</v>
       </c>
@@ -776,7 +776,7 @@
         <v>7.0195459773816866</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>28000000</v>
       </c>
@@ -793,7 +793,7 @@
         <v>7.1470472301567938</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>29000000</v>
       </c>
@@ -810,7 +810,7 @@
         <v>6.9500557807813612</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>30000000</v>
       </c>
@@ -827,7 +827,7 @@
         <v>7.1373469489518593</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>31000000</v>
       </c>
@@ -844,7 +844,7 @@
         <v>6.9340369875510026</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>32000000</v>
       </c>
@@ -861,7 +861,7 @@
         <v>7.1365665694231479</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>33000000</v>
       </c>
@@ -878,7 +878,7 @@
         <v>7.1103401177440784</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>34000000</v>
       </c>
@@ -895,7 +895,7 @@
         <v>7.1072594993253144</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>35000000</v>
       </c>
@@ -912,7 +912,7 @@
         <v>7.4028225658811859</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>36000000</v>
       </c>
@@ -929,7 +929,7 @@
         <v>6.3312822819260166</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>37000000</v>
       </c>
@@ -946,7 +946,7 @@
         <v>5.6697659670012621</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>38000000</v>
       </c>
@@ -963,7 +963,7 @@
         <v>6.276461499263748</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>39000000</v>
       </c>
@@ -980,7 +980,7 @@
         <v>6.2806334440021638</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>40000000</v>
       </c>
@@ -997,14 +997,14 @@
         <v>6.0966793342537322</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B38" s="8" t="s">
         <v>8</v>
       </c>
@@ -1015,7 +1015,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
@@ -1035,285 +1035,471 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>10000000</v>
       </c>
+      <c r="B40">
+        <v>3.07422</v>
+      </c>
       <c r="C40" s="7"/>
+      <c r="D40">
+        <v>0.19961499999999999</v>
+      </c>
       <c r="E40" s="7"/>
-      <c r="F40" t="e">
+      <c r="F40">
         <f>B40/D40</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+        <v>15.400746436891016</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>11000000</v>
       </c>
-      <c r="F41" t="e">
-        <f t="shared" ref="F41:F70" si="1">B41/D41</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B41">
+        <v>4.0935550000000003</v>
+      </c>
+      <c r="D41">
+        <v>0.208622</v>
+      </c>
+      <c r="F41">
+        <f>B41/D41</f>
+        <v>19.621875928713177</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>12000000</v>
       </c>
-      <c r="F42" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B42">
+        <v>4.904312</v>
+      </c>
+      <c r="D42">
+        <v>0.230629</v>
+      </c>
+      <c r="F42">
+        <f t="shared" ref="F42:F70" si="1">B42/D42</f>
+        <v>21.264940662275777</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>13000000</v>
       </c>
-      <c r="F43" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B43">
+        <v>5.4954840000000003</v>
+      </c>
+      <c r="D43">
+        <v>0.268316</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="1"/>
+        <v>20.481387617585238</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>14000000</v>
       </c>
-      <c r="F44" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B44">
+        <v>6.1328820000000004</v>
+      </c>
+      <c r="D44">
+        <v>0.29424</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="1"/>
+        <v>20.843128058727572</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>15000000</v>
       </c>
-      <c r="F45" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B45">
+        <v>6.7988749999999998</v>
+      </c>
+      <c r="D45">
+        <v>0.319859</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="1"/>
+        <v>21.255850234009358</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>16000000</v>
       </c>
-      <c r="F46" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B46">
+        <v>7.4492789999999998</v>
+      </c>
+      <c r="D46">
+        <v>0.374307</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="1"/>
+        <v>19.901522012679433</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>17000000</v>
       </c>
-      <c r="F47" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B47">
+        <v>7.9789300000000001</v>
+      </c>
+      <c r="D47">
+        <v>0.41203099999999998</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="1"/>
+        <v>19.364877885401828</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>18000000</v>
       </c>
-      <c r="F48" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B48">
+        <v>8.7212800000000001</v>
+      </c>
+      <c r="D48">
+        <v>0.39272200000000002</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="1"/>
+        <v>22.207261116005725</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>19000000</v>
       </c>
-      <c r="F49" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B49">
+        <v>9.3753119999999992</v>
+      </c>
+      <c r="D49">
+        <v>0.41116200000000003</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="1"/>
+        <v>22.801990456316485</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>20000000</v>
       </c>
-      <c r="F50" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B50">
+        <v>10.080152999999999</v>
+      </c>
+      <c r="D50">
+        <v>0.46141599999999999</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="1"/>
+        <v>21.846128005964246</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>21000000</v>
       </c>
-      <c r="F51" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B51">
+        <v>10.752592999999999</v>
+      </c>
+      <c r="D51">
+        <v>0.64751300000000001</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="1"/>
+        <v>16.605987833448904</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>22000000</v>
       </c>
-      <c r="F52" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B52">
+        <v>11.561036</v>
+      </c>
+      <c r="D52">
+        <v>0.73573200000000005</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="1"/>
+        <v>15.71365116645735</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>23000000</v>
       </c>
-      <c r="F53" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B53">
+        <v>12.216346</v>
+      </c>
+      <c r="D53">
+        <v>0.65195899999999996</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="1"/>
+        <v>18.737905297725778</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>24000000</v>
       </c>
-      <c r="F54" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B54">
+        <v>13.036834000000001</v>
+      </c>
+      <c r="D54">
+        <v>0.62831400000000004</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="1"/>
+        <v>20.748915351241575</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>25000000</v>
       </c>
-      <c r="F55" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B55">
+        <v>13.817802</v>
+      </c>
+      <c r="D55">
+        <v>0.62590500000000004</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="1"/>
+        <v>22.07651640424665</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>26000000</v>
       </c>
-      <c r="F56" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B56">
+        <v>14.610976000000001</v>
+      </c>
+      <c r="D56">
+        <v>0.64108600000000004</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="1"/>
+        <v>22.790976561646954</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>27000000</v>
       </c>
-      <c r="F57" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B57">
+        <v>15.201309999999999</v>
+      </c>
+      <c r="D57">
+        <v>0.68704200000000004</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="1"/>
+        <v>22.125736126757896</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>28000000</v>
       </c>
-      <c r="F58" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B58">
+        <v>16.062538</v>
+      </c>
+      <c r="D58">
+        <v>0.85647399999999996</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="1"/>
+        <v>18.754262242636671</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>29000000</v>
       </c>
-      <c r="F59" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B59">
+        <v>16.927885</v>
+      </c>
+      <c r="D59">
+        <v>0.87755899999999998</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="1"/>
+        <v>19.289740063061288</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>30000000</v>
       </c>
-      <c r="F60" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B60">
+        <v>17.821466000000001</v>
+      </c>
+      <c r="D60">
+        <v>0.91805499999999995</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="1"/>
+        <v>19.412198615551358</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>31000000</v>
       </c>
-      <c r="F61" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B61">
+        <v>18.579981</v>
+      </c>
+      <c r="D61">
+        <v>0.94625599999999999</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="1"/>
+        <v>19.635258323328994</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>32000000</v>
       </c>
-      <c r="F62" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B62">
+        <v>19.452786</v>
+      </c>
+      <c r="D62">
+        <v>0.89138200000000001</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="1"/>
+        <v>21.823175697961144</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>33000000</v>
       </c>
-      <c r="F63" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B63">
+        <v>20.361827999999999</v>
+      </c>
+      <c r="D63">
+        <v>1.0145040000000001</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="1"/>
+        <v>20.070722244564831</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>34000000</v>
       </c>
-      <c r="F64" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B64">
+        <v>21.225096000000001</v>
+      </c>
+      <c r="D64">
+        <v>1.081969</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="1"/>
+        <v>19.617101783877359</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>35000000</v>
       </c>
-      <c r="F65" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B65">
+        <v>22.179998999999999</v>
+      </c>
+      <c r="D65">
+        <v>1.1624030000000001</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="1"/>
+        <v>19.081161180760887</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>36000000</v>
       </c>
-      <c r="F66" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B66">
+        <v>23.211036</v>
+      </c>
+      <c r="D66">
+        <v>1.1323209999999999</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="1"/>
+        <v>20.498635987498247</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>37000000</v>
       </c>
-      <c r="F67" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B67">
+        <v>23.925511</v>
+      </c>
+      <c r="D67">
+        <v>1.200993</v>
+      </c>
+      <c r="F67">
+        <f>B67/D67</f>
+        <v>19.921440841037377</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>38000000</v>
       </c>
-      <c r="F68" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B68">
+        <v>24.83474</v>
+      </c>
+      <c r="D68">
+        <v>1.212243</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="1"/>
+        <v>20.486602108653134</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>39000000</v>
       </c>
-      <c r="F69" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B69">
+        <v>25.810836999999999</v>
+      </c>
+      <c r="D69">
+        <v>1.2506710000000001</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="1"/>
+        <v>20.637591340968168</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>40000000</v>
       </c>
-      <c r="F70" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="B70">
+        <v>26.719480000000001</v>
+      </c>
+      <c r="D70">
+        <v>1.263007</v>
+      </c>
+      <c r="F70">
+        <f>B70/D70</f>
+        <v>21.155448861328562</v>
       </c>
     </row>
   </sheetData>
@@ -1330,20 +1516,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2B590C-628F-42C3-BA14-2549B4CA5D44}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="22.6328125" customWidth="1"/>
-    <col min="6" max="6" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.6328125" customWidth="1"/>
+    <col min="1" max="5" width="22.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1357,7 +1543,7 @@
       </c>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1380,7 +1566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1404,7 +1590,7 @@
         <v>7.352087</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1428,7 +1614,7 @@
         <v>6.3732189999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>8</v>
       </c>
@@ -1452,7 +1638,7 @@
         <v>6.6873300000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>16</v>
       </c>
@@ -1476,7 +1662,7 @@
         <v>6.7687369999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>32</v>
       </c>
@@ -1500,7 +1686,7 @@
         <v>7.2332419999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>64</v>
       </c>
@@ -1524,17 +1710,17 @@
         <v>6.5813569999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1548,7 +1734,7 @@
       </c>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1571,13 +1757,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
       <c r="B16">
         <f>'Testing 1'!$B$40</f>
-        <v>0</v>
+        <v>3.07422</v>
       </c>
       <c r="C16">
         <v>1.7803150000000001</v>
@@ -1587,7 +1773,7 @@
       </c>
       <c r="E16">
         <f>B16/C16</f>
-        <v>0</v>
+        <v>1.7267843050246725</v>
       </c>
       <c r="F16" s="5">
         <v>1.540073</v>
@@ -1596,13 +1782,13 @@
         <v>6.6633519999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>4</v>
       </c>
       <c r="B17">
         <f>'Testing 1'!$B$40</f>
-        <v>0</v>
+        <v>3.07422</v>
       </c>
       <c r="C17">
         <v>0.91214399999999995</v>
@@ -1612,7 +1798,7 @@
       </c>
       <c r="E17">
         <f t="shared" ref="E17:E21" si="1">B17/C17</f>
-        <v>0</v>
+        <v>3.3703231068778616</v>
       </c>
       <c r="F17" s="5">
         <v>1.2319119999999999</v>
@@ -1621,13 +1807,13 @@
         <v>6.6738819999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>8</v>
       </c>
       <c r="B18">
         <f>'Testing 1'!$B$40</f>
-        <v>0</v>
+        <v>3.07422</v>
       </c>
       <c r="C18">
         <v>0.41222500000000001</v>
@@ -1637,7 +1823,7 @@
       </c>
       <c r="E18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7.4576262963187574</v>
       </c>
       <c r="F18" s="5">
         <v>1.4754229999999999</v>
@@ -1646,13 +1832,13 @@
         <v>6.1407610000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19">
         <f>'Testing 1'!$B$40</f>
-        <v>0</v>
+        <v>3.07422</v>
       </c>
       <c r="C19">
         <v>0.248222</v>
@@ -1662,7 +1848,7 @@
       </c>
       <c r="E19">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12.384961848667725</v>
       </c>
       <c r="F19" s="5">
         <v>1.988049</v>
@@ -1671,13 +1857,13 @@
         <v>7.3005849999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>32</v>
       </c>
       <c r="B20">
         <f>'Testing 1'!$B$40</f>
-        <v>0</v>
+        <v>3.07422</v>
       </c>
       <c r="C20">
         <v>0.18618000000000001</v>
@@ -1687,7 +1873,7 @@
       </c>
       <c r="E20">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.512085078955849</v>
       </c>
       <c r="F20" s="5">
         <v>1.7018230000000001</v>
@@ -1696,13 +1882,13 @@
         <v>7.0630740000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>64</v>
       </c>
       <c r="B21">
         <f>'Testing 1'!$B$40</f>
-        <v>0</v>
+        <v>3.07422</v>
       </c>
       <c r="C21">
         <v>0.175349</v>
@@ -1712,7 +1898,7 @@
       </c>
       <c r="E21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.532007596279421</v>
       </c>
       <c r="F21" s="5">
         <v>1.561496</v>

--- a/RunningTimeRecord.xlsx
+++ b/RunningTimeRecord.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD1F3FF-A27F-4FFC-A751-9FB56DBEEBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
@@ -427,19 +427,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="6" width="22.6640625" customWidth="1"/>
+    <col min="1" max="6" width="22.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
@@ -450,7 +450,7 @@
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -470,7 +470,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>10000000</v>
       </c>
@@ -487,7 +487,7 @@
         <v>6.3579792144501885</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>11000000</v>
       </c>
@@ -504,7 +504,7 @@
         <v>6.2373184762851057</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>12000000</v>
       </c>
@@ -521,7 +521,7 @@
         <v>6.4430587250201956</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>13000000</v>
       </c>
@@ -538,7 +538,7 @@
         <v>6.4812014738078716</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>14000000</v>
       </c>
@@ -555,7 +555,7 @@
         <v>6.3272796774118358</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>15000000</v>
       </c>
@@ -572,7 +572,7 @@
         <v>6.4731204659417916</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>16000000</v>
       </c>
@@ -589,7 +589,7 @@
         <v>6.4997078709270468</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>17000000</v>
       </c>
@@ -606,7 +606,7 @@
         <v>6.5515861482115554</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>18000000</v>
       </c>
@@ -623,7 +623,7 @@
         <v>7.0727800857430747</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>19000000</v>
       </c>
@@ -640,7 +640,7 @@
         <v>7.1319490965991053</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>20000000</v>
       </c>
@@ -657,7 +657,7 @@
         <v>7.0679969840807439</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>21000000</v>
       </c>
@@ -674,7 +674,7 @@
         <v>6.9647987352888778</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>22000000</v>
       </c>
@@ -691,7 +691,7 @@
         <v>6.708556546916709</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>23000000</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7.2916027724958603</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>24000000</v>
       </c>
@@ -725,7 +725,7 @@
         <v>6.9669498365818487</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>25000000</v>
       </c>
@@ -742,7 +742,7 @@
         <v>7.0572231549324718</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>26000000</v>
       </c>
@@ -759,7 +759,7 @@
         <v>7.2198789788533801</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>27000000</v>
       </c>
@@ -776,7 +776,7 @@
         <v>7.0195459773816866</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>28000000</v>
       </c>
@@ -793,7 +793,7 @@
         <v>7.1470472301567938</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>29000000</v>
       </c>
@@ -810,7 +810,7 @@
         <v>6.9500557807813612</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>30000000</v>
       </c>
@@ -827,7 +827,7 @@
         <v>7.1373469489518593</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>31000000</v>
       </c>
@@ -844,7 +844,7 @@
         <v>6.9340369875510026</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>32000000</v>
       </c>
@@ -861,7 +861,7 @@
         <v>7.1365665694231479</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>33000000</v>
       </c>
@@ -878,7 +878,7 @@
         <v>7.1103401177440784</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>34000000</v>
       </c>
@@ -895,7 +895,7 @@
         <v>7.1072594993253144</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>35000000</v>
       </c>
@@ -912,7 +912,7 @@
         <v>7.4028225658811859</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>36000000</v>
       </c>
@@ -929,7 +929,7 @@
         <v>6.3312822819260166</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>37000000</v>
       </c>
@@ -946,7 +946,7 @@
         <v>5.6697659670012621</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>38000000</v>
       </c>
@@ -963,7 +963,7 @@
         <v>6.276461499263748</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>39000000</v>
       </c>
@@ -980,7 +980,7 @@
         <v>6.2806334440021638</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>40000000</v>
       </c>
@@ -997,14 +997,14 @@
         <v>6.0966793342537322</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B38" s="8" t="s">
         <v>8</v>
       </c>
@@ -1015,7 +1015,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>10000000</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>15.400746436891016</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>11000000</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>19.621875928713177</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>12000000</v>
       </c>
@@ -1078,11 +1078,11 @@
         <v>0.230629</v>
       </c>
       <c r="F42">
-        <f t="shared" ref="F42:F70" si="1">B42/D42</f>
+        <f t="shared" ref="F42:F69" si="1">B42/D42</f>
         <v>21.264940662275777</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>13000000</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>20.481387617585238</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>14000000</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>20.843128058727572</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>15000000</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>21.255850234009358</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>16000000</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>19.901522012679433</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>17000000</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>19.364877885401828</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>18000000</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>22.207261116005725</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>19000000</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>22.801990456316485</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>20000000</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>21.846128005964246</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>21000000</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>16.605987833448904</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>22000000</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>15.71365116645735</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>23000000</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>18.737905297725778</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>24000000</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>20.748915351241575</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>25000000</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>22.07651640424665</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>26000000</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>22.790976561646954</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>27000000</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>22.125736126757896</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>28000000</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>18.754262242636671</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>29000000</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>19.289740063061288</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>30000000</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>19.412198615551358</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>31000000</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>19.635258323328994</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>32000000</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>21.823175697961144</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>33000000</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>20.070722244564831</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>34000000</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>19.617101783877359</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>35000000</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>19.081161180760887</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>36000000</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>20.498635987498247</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>37000000</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>19.921440841037377</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>38000000</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>20.486602108653134</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>39000000</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>20.637591340968168</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>40000000</v>
       </c>
@@ -1516,20 +1516,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2B590C-628F-42C3-BA14-2549B4CA5D44}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="5" width="22.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.6640625" customWidth="1"/>
+    <col min="1" max="5" width="22.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>7.352087</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>6.3732189999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>8</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>6.6873300000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>16</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>6.7687369999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>32</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>7.2332419999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>64</v>
       </c>
@@ -1710,17 +1710,17 @@
         <v>6.5813569999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>6.6633519999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>4</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>6.6738819999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>8</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>6.1407610000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>7.3005849999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>32</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>7.0630740000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>64</v>
       </c>

--- a/RunningTimeRecord.xlsx
+++ b/RunningTimeRecord.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD1F3FF-A27F-4FFC-A751-9FB56DBEEBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D913F6-8284-41CB-ACC7-2B02AA064671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="15">
   <si>
     <t>n</t>
   </si>
@@ -77,6 +77,12 @@
   <si>
     <t>Serial Code (Baseline)</t>
   </si>
+  <si>
+    <t>OpenMP</t>
+  </si>
+  <si>
+    <t>OpenMp</t>
+  </si>
 </sst>
 </file>
 
@@ -91,7 +97,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -110,6 +116,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -123,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -140,8 +158,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -426,41 +456,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K70"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="22.6328125" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" style="10" customWidth="1"/>
+    <col min="5" max="6" width="22.6640625" customWidth="1"/>
+    <col min="8" max="8" width="22.109375" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="8"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="13"/>
+      <c r="D3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -469,16 +510,19 @@
       <c r="F4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H4" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>10000000</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="10">
         <v>4.221819</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5">
+      <c r="D5" s="10">
         <v>0.66401900000000003</v>
       </c>
       <c r="E5" s="7"/>
@@ -487,15 +531,15 @@
         <v>6.3579792144501885</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>11000000</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="10">
         <v>4.7456699999999996</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6">
+      <c r="D6" s="10">
         <v>0.76085100000000006</v>
       </c>
       <c r="E6" s="7"/>
@@ -504,15 +548,15 @@
         <v>6.2373184762851057</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>12000000</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="10">
         <v>5.4632949999999996</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7">
+      <c r="D7" s="10">
         <v>0.84793499999999999</v>
       </c>
       <c r="E7" s="7"/>
@@ -521,15 +565,15 @@
         <v>6.4430587250201956</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>13000000</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="10">
         <v>6.0686730000000004</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8">
+      <c r="D8" s="10">
         <v>0.93635000000000002</v>
       </c>
       <c r="E8" s="7"/>
@@ -538,15 +582,15 @@
         <v>6.4812014738078716</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>14000000</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="10">
         <v>6.7864820000000003</v>
       </c>
       <c r="C9" s="7"/>
-      <c r="D9">
+      <c r="D9" s="10">
         <v>1.0725750000000001</v>
       </c>
       <c r="E9" s="7"/>
@@ -555,15 +599,15 @@
         <v>6.3272796774118358</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>15000000</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="10">
         <v>7.5130920000000003</v>
       </c>
       <c r="C10" s="7"/>
-      <c r="D10">
+      <c r="D10" s="10">
         <v>1.16066</v>
       </c>
       <c r="E10" s="7"/>
@@ -572,15 +616,15 @@
         <v>6.4731204659417916</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>16000000</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="10">
         <v>8.2434170000000009</v>
       </c>
       <c r="C11" s="7"/>
-      <c r="D11">
+      <c r="D11" s="10">
         <v>1.268275</v>
       </c>
       <c r="E11" s="7"/>
@@ -589,15 +633,15 @@
         <v>6.4997078709270468</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>17000000</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="10">
         <v>9.0389809999999997</v>
       </c>
       <c r="C12" s="7"/>
-      <c r="D12">
+      <c r="D12" s="10">
         <v>1.3796630000000001</v>
       </c>
       <c r="E12" s="7"/>
@@ -606,15 +650,15 @@
         <v>6.5515861482115554</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>18000000</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="10">
         <v>11.076497</v>
       </c>
       <c r="C13" s="7"/>
-      <c r="D13">
+      <c r="D13" s="10">
         <v>1.566074</v>
       </c>
       <c r="E13" s="7"/>
@@ -623,15 +667,15 @@
         <v>7.0727800857430747</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>19000000</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="10">
         <v>11.668153999999999</v>
       </c>
       <c r="C14" s="7"/>
-      <c r="D14">
+      <c r="D14" s="10">
         <v>1.6360399999999999</v>
       </c>
       <c r="E14" s="7"/>
@@ -640,15 +684,15 @@
         <v>7.1319490965991053</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>20000000</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="10">
         <v>12.374013</v>
       </c>
       <c r="C15" s="7"/>
-      <c r="D15">
+      <c r="D15" s="10">
         <v>1.75071</v>
       </c>
       <c r="E15" s="7"/>
@@ -657,15 +701,15 @@
         <v>7.0679969840807439</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>21000000</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="10">
         <v>13.410712999999999</v>
       </c>
       <c r="C16" s="7"/>
-      <c r="D16">
+      <c r="D16" s="10">
         <v>1.9254990000000001</v>
       </c>
       <c r="E16" s="7"/>
@@ -674,15 +718,15 @@
         <v>6.9647987352888778</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>22000000</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="10">
         <v>13.503204</v>
       </c>
       <c r="C17" s="7"/>
-      <c r="D17">
+      <c r="D17" s="10">
         <v>2.0128330000000001</v>
       </c>
       <c r="E17" s="7"/>
@@ -691,15 +735,15 @@
         <v>6.708556546916709</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>23000000</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="10">
         <v>15.334875</v>
       </c>
       <c r="C18" s="7"/>
-      <c r="D18">
+      <c r="D18" s="10">
         <v>2.1030869999999999</v>
       </c>
       <c r="E18" s="7"/>
@@ -708,15 +752,15 @@
         <v>7.2916027724958603</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>24000000</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="10">
         <v>15.795399</v>
       </c>
       <c r="C19" s="7"/>
-      <c r="D19">
+      <c r="D19" s="10">
         <v>2.2671899999999998</v>
       </c>
       <c r="E19" s="7"/>
@@ -725,15 +769,15 @@
         <v>6.9669498365818487</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>25000000</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="10">
         <v>17.032720999999999</v>
       </c>
       <c r="C20" s="7"/>
-      <c r="D20">
+      <c r="D20" s="10">
         <v>2.413516</v>
       </c>
       <c r="E20" s="7"/>
@@ -742,15 +786,15 @@
         <v>7.0572231549324718</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>26000000</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="10">
         <v>18.229096999999999</v>
       </c>
       <c r="C21" s="7"/>
-      <c r="D21">
+      <c r="D21" s="10">
         <v>2.524848</v>
       </c>
       <c r="E21" s="7"/>
@@ -759,15 +803,15 @@
         <v>7.2198789788533801</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>27000000</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="10">
         <v>19.070878</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22">
+      <c r="D22" s="10">
         <v>2.716825</v>
       </c>
       <c r="E22" s="7"/>
@@ -776,15 +820,15 @@
         <v>7.0195459773816866</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>28000000</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="10">
         <v>20.289345000000001</v>
       </c>
       <c r="C23" s="7"/>
-      <c r="D23">
+      <c r="D23" s="10">
         <v>2.8388429999999998</v>
       </c>
       <c r="E23" s="7"/>
@@ -793,15 +837,15 @@
         <v>7.1470472301567938</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>29000000</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="10">
         <v>20.676687000000001</v>
       </c>
       <c r="C24" s="7"/>
-      <c r="D24">
+      <c r="D24" s="10">
         <v>2.9750390000000002</v>
       </c>
       <c r="E24" s="7"/>
@@ -810,15 +854,15 @@
         <v>6.9500557807813612</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>30000000</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="10">
         <v>21.899799999999999</v>
       </c>
       <c r="C25" s="7"/>
-      <c r="D25">
+      <c r="D25" s="10">
         <v>3.0683389999999999</v>
       </c>
       <c r="E25" s="7"/>
@@ -827,15 +871,15 @@
         <v>7.1373469489518593</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>31000000</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="10">
         <v>22.377856999999999</v>
       </c>
       <c r="C26" s="7"/>
-      <c r="D26">
+      <c r="D26" s="10">
         <v>3.2272479999999999</v>
       </c>
       <c r="E26" s="7"/>
@@ -844,15 +888,15 @@
         <v>6.9340369875510026</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>32000000</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="10">
         <v>24.132621</v>
       </c>
       <c r="C27" s="7"/>
-      <c r="D27">
+      <c r="D27" s="10">
         <v>3.381545</v>
       </c>
       <c r="E27" s="7"/>
@@ -861,15 +905,15 @@
         <v>7.1365665694231479</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>33000000</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="10">
         <v>24.831582999999998</v>
       </c>
       <c r="C28" s="7"/>
-      <c r="D28">
+      <c r="D28" s="10">
         <v>3.4923199999999999</v>
       </c>
       <c r="E28" s="7"/>
@@ -878,15 +922,15 @@
         <v>7.1103401177440784</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>34000000</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="10">
         <v>26.061553</v>
       </c>
       <c r="C29" s="7"/>
-      <c r="D29">
+      <c r="D29" s="10">
         <v>3.6668919999999998</v>
       </c>
       <c r="E29" s="7"/>
@@ -895,15 +939,15 @@
         <v>7.1072594993253144</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>35000000</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="10">
         <v>27.901105000000001</v>
       </c>
       <c r="C30" s="7"/>
-      <c r="D30">
+      <c r="D30" s="10">
         <v>3.7689819999999998</v>
       </c>
       <c r="E30" s="7"/>
@@ -912,15 +956,15 @@
         <v>7.4028225658811859</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>36000000</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="10">
         <v>28.604783999999999</v>
       </c>
       <c r="C31" s="7"/>
-      <c r="D31">
+      <c r="D31" s="10">
         <v>4.518008</v>
       </c>
       <c r="E31" s="7"/>
@@ -929,15 +973,15 @@
         <v>6.3312822819260166</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>37000000</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="10">
         <v>29.860191</v>
       </c>
       <c r="C32" s="7"/>
-      <c r="D32">
+      <c r="D32" s="10">
         <v>5.2665649999999999</v>
       </c>
       <c r="E32" s="7"/>
@@ -946,15 +990,15 @@
         <v>5.6697659670012621</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>38000000</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="10">
         <v>30.595779</v>
       </c>
       <c r="C33" s="7"/>
-      <c r="D33">
+      <c r="D33" s="10">
         <v>4.8746859999999996</v>
       </c>
       <c r="E33" s="7"/>
@@ -963,15 +1007,15 @@
         <v>6.276461499263748</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>39000000</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="10">
         <v>30.810445000000001</v>
       </c>
       <c r="C34" s="7"/>
-      <c r="D34">
+      <c r="D34" s="10">
         <v>4.905627</v>
       </c>
       <c r="E34" s="7"/>
@@ -980,15 +1024,15 @@
         <v>6.2806334440021638</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>40000000</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="10">
         <v>32.276363000000003</v>
       </c>
       <c r="C35" s="7"/>
-      <c r="D35">
+      <c r="D35" s="10">
         <v>5.2940889999999996</v>
       </c>
       <c r="E35" s="7"/>
@@ -997,35 +1041,49 @@
         <v>6.0966793342537322</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B38" s="8" t="s">
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B38" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8" t="s">
+      <c r="C38" s="13"/>
+      <c r="D38" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E39" s="6" t="s">
@@ -1034,16 +1092,19 @@
       <c r="F39" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H39" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>10000000</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="10">
         <v>3.07422</v>
       </c>
       <c r="C40" s="7"/>
-      <c r="D40">
+      <c r="D40" s="10">
         <v>0.19961499999999999</v>
       </c>
       <c r="E40" s="7"/>
@@ -1051,463 +1112,559 @@
         <f>B40/D40</f>
         <v>15.400746436891016</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H40" s="10">
+        <v>0.216973</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>11000000</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="10">
         <v>4.0935550000000003</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="10">
         <v>0.208622</v>
       </c>
       <c r="F41">
         <f>B41/D41</f>
         <v>19.621875928713177</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H41" s="10">
+        <v>0.21165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>12000000</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="10">
         <v>4.904312</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="10">
         <v>0.230629</v>
       </c>
       <c r="F42">
         <f t="shared" ref="F42:F69" si="1">B42/D42</f>
         <v>21.264940662275777</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H42" s="10">
+        <v>0.245451</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>13000000</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="10">
         <v>5.4954840000000003</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="10">
         <v>0.268316</v>
       </c>
       <c r="F43">
         <f t="shared" si="1"/>
         <v>20.481387617585238</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H43" s="10">
+        <v>0.25640299999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>14000000</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="10">
         <v>6.1328820000000004</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="10">
         <v>0.29424</v>
       </c>
       <c r="F44">
         <f t="shared" si="1"/>
         <v>20.843128058727572</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H44" s="10">
+        <v>0.28809899999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>15000000</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="10">
         <v>6.7988749999999998</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="10">
         <v>0.319859</v>
       </c>
       <c r="F45">
         <f t="shared" si="1"/>
         <v>21.255850234009358</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H45" s="10">
+        <v>0.329737</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>16000000</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="10">
         <v>7.4492789999999998</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="10">
         <v>0.374307</v>
       </c>
       <c r="F46">
         <f t="shared" si="1"/>
         <v>19.901522012679433</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H46" s="10">
+        <v>0.34054099999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>17000000</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="10">
         <v>7.9789300000000001</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="10">
         <v>0.41203099999999998</v>
       </c>
       <c r="F47">
         <f t="shared" si="1"/>
         <v>19.364877885401828</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H47" s="10">
+        <v>0.37627100000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>18000000</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="10">
         <v>8.7212800000000001</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="10">
         <v>0.39272200000000002</v>
       </c>
       <c r="F48">
         <f t="shared" si="1"/>
         <v>22.207261116005725</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H48" s="10">
+        <v>0.39349200000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>19000000</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="10">
         <v>9.3753119999999992</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="10">
         <v>0.41116200000000003</v>
       </c>
       <c r="F49">
         <f t="shared" si="1"/>
         <v>22.801990456316485</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H49" s="10">
+        <v>0.42541000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>20000000</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="10">
         <v>10.080152999999999</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="10">
         <v>0.46141599999999999</v>
       </c>
       <c r="F50">
         <f t="shared" si="1"/>
         <v>21.846128005964246</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H50" s="10">
+        <v>0.44863900000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>21000000</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="10">
         <v>10.752592999999999</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="10">
         <v>0.64751300000000001</v>
       </c>
       <c r="F51">
         <f t="shared" si="1"/>
         <v>16.605987833448904</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H51" s="10">
+        <v>0.459978</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>22000000</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="10">
         <v>11.561036</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="10">
         <v>0.73573200000000005</v>
       </c>
       <c r="F52">
         <f t="shared" si="1"/>
         <v>15.71365116645735</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H52" s="10">
+        <v>0.50284499999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>23000000</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="10">
         <v>12.216346</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="10">
         <v>0.65195899999999996</v>
       </c>
       <c r="F53">
         <f t="shared" si="1"/>
         <v>18.737905297725778</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H53" s="10">
+        <v>0.53020299999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>24000000</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="10">
         <v>13.036834000000001</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="10">
         <v>0.62831400000000004</v>
       </c>
       <c r="F54">
         <f t="shared" si="1"/>
         <v>20.748915351241575</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H54" s="10">
+        <v>0.55043200000000003</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>25000000</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="10">
         <v>13.817802</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="10">
         <v>0.62590500000000004</v>
       </c>
       <c r="F55">
         <f t="shared" si="1"/>
         <v>22.07651640424665</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H55" s="10">
+        <v>0.60006199999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>26000000</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="10">
         <v>14.610976000000001</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="10">
         <v>0.64108600000000004</v>
       </c>
       <c r="F56">
         <f t="shared" si="1"/>
         <v>22.790976561646954</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H56" s="10">
+        <v>0.68986199999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>27000000</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="10">
         <v>15.201309999999999</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="10">
         <v>0.68704200000000004</v>
       </c>
       <c r="F57">
         <f t="shared" si="1"/>
         <v>22.125736126757896</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H57" s="10">
+        <v>0.64302199999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>28000000</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="10">
         <v>16.062538</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="10">
         <v>0.85647399999999996</v>
       </c>
       <c r="F58">
         <f t="shared" si="1"/>
         <v>18.754262242636671</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H58" s="10">
+        <v>0.71674599999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>29000000</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="10">
         <v>16.927885</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="10">
         <v>0.87755899999999998</v>
       </c>
       <c r="F59">
         <f t="shared" si="1"/>
         <v>19.289740063061288</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H59" s="10">
+        <v>0.73519000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>30000000</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="10">
         <v>17.821466000000001</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="10">
         <v>0.91805499999999995</v>
       </c>
       <c r="F60">
         <f t="shared" si="1"/>
         <v>19.412198615551358</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H60" s="10">
+        <v>0.89686399999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>31000000</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="10">
         <v>18.579981</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="10">
         <v>0.94625599999999999</v>
       </c>
       <c r="F61">
         <f t="shared" si="1"/>
         <v>19.635258323328994</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H61" s="10">
+        <v>0.85248999999999997</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>32000000</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="10">
         <v>19.452786</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="10">
         <v>0.89138200000000001</v>
       </c>
       <c r="F62">
         <f t="shared" si="1"/>
         <v>21.823175697961144</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H62" s="10">
+        <v>0.96400200000000003</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>33000000</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="10">
         <v>20.361827999999999</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="10">
         <v>1.0145040000000001</v>
       </c>
       <c r="F63">
         <f t="shared" si="1"/>
         <v>20.070722244564831</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H63" s="10">
+        <v>0.87285800000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>34000000</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="10">
         <v>21.225096000000001</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="10">
         <v>1.081969</v>
       </c>
       <c r="F64">
         <f t="shared" si="1"/>
         <v>19.617101783877359</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H64" s="10">
+        <v>0.89015500000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>35000000</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="10">
         <v>22.179998999999999</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="10">
         <v>1.1624030000000001</v>
       </c>
       <c r="F65">
         <f t="shared" si="1"/>
         <v>19.081161180760887</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H65" s="10">
+        <v>0.985043</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>36000000</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="10">
         <v>23.211036</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="10">
         <v>1.1323209999999999</v>
       </c>
       <c r="F66">
         <f t="shared" si="1"/>
         <v>20.498635987498247</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H66" s="10">
+        <v>1.027749</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>37000000</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="10">
         <v>23.925511</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="10">
         <v>1.200993</v>
       </c>
       <c r="F67">
         <f>B67/D67</f>
         <v>19.921440841037377</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H67" s="10">
+        <v>1.011207</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>38000000</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="10">
         <v>24.83474</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="10">
         <v>1.212243</v>
       </c>
       <c r="F68">
         <f t="shared" si="1"/>
         <v>20.486602108653134</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H68" s="10">
+        <v>1.143842</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>39000000</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="10">
         <v>25.810836999999999</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="10">
         <v>1.2506710000000001</v>
       </c>
       <c r="F69">
         <f t="shared" si="1"/>
         <v>20.637591340968168</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" s="2">
+      <c r="H69" s="10">
+        <v>1.156982</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="11">
         <v>40000000</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="12">
         <v>26.719480000000001</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="12">
         <v>1.263007</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="12">
         <f>B70/D70</f>
         <v>21.155448861328562</v>
       </c>
+      <c r="H70" s="12">
+        <v>1.105423</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="D38:F38"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="A37:K37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1516,34 +1673,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2B590C-628F-42C3-BA14-2549B4CA5D44}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="22.6328125" customWidth="1"/>
-    <col min="6" max="6" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.6328125" customWidth="1"/>
+    <col min="1" max="5" width="22.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9" t="s">
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="9"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G3" s="15"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1566,7 +1723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1590,7 +1747,7 @@
         <v>7.352087</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1614,7 +1771,7 @@
         <v>6.3732189999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>8</v>
       </c>
@@ -1638,7 +1795,7 @@
         <v>6.6873300000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>16</v>
       </c>
@@ -1662,7 +1819,7 @@
         <v>6.7687369999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>32</v>
       </c>
@@ -1686,7 +1843,7 @@
         <v>7.2332419999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>64</v>
       </c>
@@ -1710,31 +1867,31 @@
         <v>6.5813569999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9" t="s">
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="9"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G14" s="15"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1757,7 +1914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -1782,7 +1939,7 @@
         <v>6.6633519999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>4</v>
       </c>
@@ -1807,7 +1964,7 @@
         <v>6.6738819999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>8</v>
       </c>
@@ -1832,7 +1989,7 @@
         <v>6.1407610000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1857,7 +2014,7 @@
         <v>7.3005849999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>32</v>
       </c>
@@ -1882,7 +2039,7 @@
         <v>7.0630740000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>64</v>
       </c>
